--- a/findprice_products_2.xlsx
+++ b/findprice_products_2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\automated-EC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\auto-EC-process\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -141,808 +141,809 @@
     <t>https://www.findprice.com.tw/go/gxb7z8w67bh/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
   </si>
   <si>
+    <t>$ 41,590</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gsbi935fxxn/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>APPLE MacBook Air M2 8G 256G 15吋 銀 MQKR3TA/A</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gcfjx8zdqcs/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>APPLE MacBook Air M2 8G 256G 13吋 午夜 MLY33TA/A</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gfmfz827zeh/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>APPLE MacBook Air M2 8G 256G 15吋 星光 MQKU3TA/A</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gm72j7csdnt/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>APPLE MacBook Air M2 8G 256G 15吋 午夜 MQKW3TA/A</t>
+  </si>
+  <si>
+    <t>$ 42,500</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gebmj29ghtv/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>APPLE MacBook Air M2 8G 256G 13吋 星光 MLY13TA/A</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/grvdgddrwbu/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M2/8G/512G/太空灰 MLXX3TA/A 限量促銷</t>
+  </si>
+  <si>
+    <t>$ 45,100</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/ga6zndsxxei/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>樂天市場 - COMDEX印表機專賣店</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/ghhh59ep57m/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>蝦皮購物精選 - 點子3C 二手3C專賣店</t>
+  </si>
+  <si>
+    <t>全館最高折1000元「點子3C」Apple MacBook Air 15吋 M2 8G 256G 2023年 A2941</t>
+  </si>
+  <si>
+    <t>$ 20,580</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gwzwj6ahnwx/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
+  </si>
+  <si>
+    <t>Apple 原廠 MagSafe 充電器</t>
+  </si>
+  <si>
+    <t>【Apple】原廠新款 MagSafe 充電器 - 1公尺 (A2580)</t>
+  </si>
+  <si>
+    <t>$ 1,250</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gz3advj5jhr/?s=0&amp;f=d&amp;t=14&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>鮮拾</t>
+  </si>
+  <si>
+    <t>【Apple】原廠MagSafe充電器</t>
+  </si>
+  <si>
+    <t>$ 1,238</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gfzsv8izum9/?s=0&amp;f=d&amp;t=14&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gfzsv8izum9/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple 原廠公司貨A3250 / MagSafe 充電器-200cm (2024新款盒裝)</t>
+  </si>
+  <si>
+    <t>$ 1,613</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g56tmnahe7y/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>【Apple】原廠新款 MagSafe 充電器 - 2公尺 (A3250)</t>
+  </si>
+  <si>
+    <t>$ 1,750</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gn7bsf234j3/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>【全新品 包裝已拆】Apple 原廠 MagSafe 充電器 MHXH3TA/A (臺灣公司貨)</t>
+  </si>
+  <si>
+    <t>$ 1,099</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/geey8ie436g/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>樂天市場 - Mr ORIGINAL</t>
+  </si>
+  <si>
+    <t>Apple 原廠 MagSafe 充電器 A3502</t>
+  </si>
+  <si>
+    <t>$ 1,260</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gaxzhwtg2js/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple 原廠 MagSafe 充電器 (2 公尺) A3502</t>
+  </si>
+  <si>
+    <t>$ 1,760</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gevqz8p82nc/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple 原廠 MagSafe 充電器 1m (MX6X3TA/A) 白</t>
+  </si>
+  <si>
+    <t>$ 1,290</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g4begc6962j/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>myfone 網路門市</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gz3advj5jhr/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple原廠 MagSafe充電器1m (MX6X3TA/A)-白</t>
+  </si>
+  <si>
+    <t>$ 1,190</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g3pvzxcp5u6/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple 原廠公司貨A2580 / MagSafe 充電器-100cm (2024新款盒裝)</t>
+  </si>
+  <si>
+    <t>$ 1,135</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gcjsttf223z/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gfk99njxnpz/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>蝦皮購物精選 - CASESSI 購物</t>
+  </si>
+  <si>
+    <t>Apple 蘋果保固一年 新款MagSafe 充電器-2M / A3250【原廠盒裝】</t>
+  </si>
+  <si>
+    <t>$ 1,612</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g4f32iutdmy/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple 蘋果 原廠新款 MagSafe 充電器 - 1公尺 (A2580)</t>
+  </si>
+  <si>
+    <t>$ 1,218</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/giy8rjzrkhc/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Global Mall 環球 Online</t>
+  </si>
+  <si>
+    <t>Apple蘋果 臺灣原廠官方正品 MagSafe 充電器 (1 公尺)【原廠保固一年】A2580 / 2024最新款</t>
+  </si>
+  <si>
+    <t>$ 1,289</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gp5td25ppac/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - NOKIA品牌專賣店</t>
+  </si>
+  <si>
+    <t>Apple MagSafe Charger 充電器 原廠 公司貨 保證正品</t>
+  </si>
+  <si>
+    <t>$ 950</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gi6vrdy6vyc/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - Mr.Reset | 3C 福利品的銷售專家</t>
+  </si>
+  <si>
+    <t>Apple 原廠 MagSafe 雙充電器 (MHXF3TA/A) 展示品</t>
+  </si>
+  <si>
+    <t>$ 2,600</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/ge4u8kk6up8/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>$ 1,136</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gdu92tv8xqa/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple 蘋果保固一年 新款MagSafe 充電器-1M / A2580【原廠盒裝】</t>
+  </si>
+  <si>
+    <t>$ 1,134</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gbvg9uz2px7/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple 臺灣原廠盒裝新款 MagSafe 充電器-1M【A2580】支援iPhone 17/16系列</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gp5kwh4xypu/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>Apple 蘋果 原廠新款 MagSafe 充電器 - 2公尺 (A3250)</t>
+  </si>
+  <si>
+    <t>$ 1,614</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gmzcxqaesp6/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
+  </si>
+  <si>
+    <t>OPPO Reno8 Pro 5G</t>
+  </si>
+  <si>
+    <t>【OPPO】A級福利品 Reno8 Pro 5G 6.7吋(12G/256G)</t>
+  </si>
+  <si>
+    <t>$ 5,590</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g9yptu4svqi/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20reno8%20pro%205g</t>
+  </si>
+  <si>
+    <t>$ 5,211</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g75seveppud/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%20pro%205g</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g9yptu4svqi/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%20pro%205g</t>
+  </si>
+  <si>
+    <t>OPPO Reno8 Pro 12G/256G 6.7吋 5G 智慧手機 公司貨 Reno 8 福利品【ET手機倉庫】</t>
+  </si>
+  <si>
+    <t>$ 5,590～7,500</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g4w88rwr3xt/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%20pro%205g</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - ET手機倉庫</t>
+  </si>
+  <si>
+    <t>博客來</t>
+  </si>
+  <si>
+    <t>【樂曄通訊】OPPO Reno8 Pro 5G 12G/256G 凝光綠 6.7吋 超級閃充 超強夜拍 全新未拆保固一年</t>
+  </si>
+  <si>
+    <t>$ 16,200</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gbjfsb3v8ki/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%20pro%205g</t>
+  </si>
+  <si>
+    <t>OPPO Reno8 5G</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g75seveppud/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>【OPPO】Reno8 (12G/256G) 5G 智慧手機 (S+級福利品)</t>
+  </si>
+  <si>
+    <t>$ 4,811</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gbwdkma64nu/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>【樂曄通訊】OPPO Reno8 T 5G 8GB/128GB 首款億級畫素 6.7吋 67W超級閃充 全新未拆一年保固</t>
+  </si>
+  <si>
+    <t>$ 8,500</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g8z556jvhqk/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>OPPO Reno8 8G/256G 6.4吋 5G 智慧手機 Reno 8 福利品【ET手機倉庫】</t>
+  </si>
+  <si>
+    <t>$ 5,500～7,300</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gjr9uw7244w/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>【賀運福利品】OPPO Reno8 5G 6.4吋</t>
+  </si>
+  <si>
+    <t>$ 3,611～3,811</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gwifu8n9cd2/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - Hold Win賀運認證福利機</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gbwdkma64nu/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>【OPPO】B+級福利品 Reno8 5G 6.4吋(8G/256G)</t>
+  </si>
+  <si>
+    <t>$ 3,411</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/ggzst3nzjxh/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g75seveppud/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>【OPPO】A+級福利品 Reno8 5G 6.4吋(8G/256G)</t>
+  </si>
+  <si>
+    <t>$ 4,999</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g8zqmkddw9f/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>【OPPO】A級福利品 Reno8 5G 6.4吋(12G/256G)</t>
+  </si>
+  <si>
+    <t>$ 5,300</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gzg9k7i5m77/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g9yptu4svqi/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>$ 3,911</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gmvmp7men9d/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>【OPPO】A級福利品 Reno8 5G 6.4吋(8G/256G)</t>
+  </si>
+  <si>
+    <t>$ 3,711</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gpn6yxef4vh/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
+  </si>
+  <si>
+    <t>OPPO A77 5G</t>
+  </si>
+  <si>
+    <t>【OPPO】【A級福利品】OPPO A77 (5G) (4+64GB)</t>
+  </si>
+  <si>
+    <t>$ 3,111</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gxthgfpwh3i/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20a77%205g</t>
+  </si>
+  <si>
+    <t>【OPPO】A級福利品 A77 5G 6.5吋(4G/64G)</t>
+  </si>
+  <si>
+    <t>$ 2,611</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g4ta9digtgn/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20a77%205g</t>
+  </si>
+  <si>
+    <t>【創宇通訊│全新品】OPPO A77 6+128GB 6.5吋 (5G) 臉部解鎖 雙卡雙待 超級閃充 大電量</t>
+  </si>
+  <si>
+    <t>$ 4,990</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gf2gawdgshm/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g4ta9digtgn/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
+  </si>
+  <si>
+    <t>【OPPO】A級福利品 A77 5G 6.5吋(6G/128G)</t>
+  </si>
+  <si>
+    <t>$ 2,911</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/ggq7kh93e8b/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gxthgfpwh3i/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
+  </si>
+  <si>
+    <t>【OPPO】A+級福利品 OPPO A77 5G 6.5吋(4G/64G)</t>
+  </si>
+  <si>
+    <t>$ 3,332</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gcmy9tnkn3t/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
+  </si>
+  <si>
+    <t>OPPO A77 (5G) 64GB 安卓13 4800萬畫素</t>
+  </si>
+  <si>
+    <t>$ 2,000</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g2p6ywmtbqz/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
+  </si>
+  <si>
+    <t>蝦皮購物精選 - 我❤️香機寶</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 14吋筆電</t>
+  </si>
+  <si>
+    <t>【Lenovo】14吋R7輕薄筆電(IdeaPad Slim 3/82XL008KTW/R7-5825U/16G/512G/W11/灰)</t>
+  </si>
+  <si>
+    <t>$ 14,111</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gvmqhzy2e76/?s=0&amp;f=d&amp;t=14&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>Lenovo 聯想 IdeaPad Slim 3 輕薄筆電 14吋 灰色 i5-13420H 512GB 8GB WIN11 Home IdeaPad Slim 3 14IRH10</t>
+  </si>
+  <si>
+    <t>$ 21,990</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gc9pmg8xnzc/?s=0&amp;f=d&amp;t=14&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】14吋i5輕薄筆電(IdeaPad Slim 3/83EL0017TW/i5-13420H/16G/512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>$ 15,111</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gtgquij3ivv/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gvmqhzy2e76/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】14吋R7輕薄筆電(IdeaPad Slim 3/82XL008JTW/R7-5825U/16G/512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gebbk96vkmr/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】Office 2024組★14吋R7輕薄筆電(IdeaPad Slim 3/82XL008JTW/R7-5825U/16G/512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>$ 18,301</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g975tdrbguk/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】微軟M365一年組★14吋R7輕薄筆電(IdeaPad Slim 3/82XL008KTW/R7-5825U/16G/512G/W11/灰)</t>
+  </si>
+  <si>
+    <t>$ 20,390</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gizwb3nk7w4/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】Office 2024組★14吋R7輕薄筆電(IdeaPad Slim 3/82XL008KTW/R7-5825U/16G/512G/W11/灰)</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gq9kc3ucrt3/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】Office 2024組★14吋i5輕薄筆電(IdeaPad Slim 3/83EL0017TW/i5-13420H/16G/512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>$ 20,301</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gbe6scefp6n/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 83K000AGTW 14吋 輕薄效能筆電</t>
+  </si>
+  <si>
+    <t>$ 16,490</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/guek92saz4p/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - 崑碁電腦專賣店</t>
+  </si>
+  <si>
+    <t>Lenovo 聯想 IdeaPad Slim 3 83K000AGTW i5/14吋 效能筆電[聊聊再優惠]</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g7ckkgzmr86/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - Kunchi崑碁電腦3C選品店</t>
+  </si>
+  <si>
+    <t>Lenovo 聯想 IdeaPad Slim 3 83EL0017TW i5/16G/512G 14吋輕薄筆電[聊聊再優</t>
+  </si>
+  <si>
+    <t>$ 16,990</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gpewszgc4si/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>Lenovo 聯想 IdeaPad Slim 3 83K90013TW R7-8840HS 14吋 輕薄筆電</t>
+  </si>
+  <si>
+    <t>$ 19,990</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gy9iuv4diwb/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - Lenovo｜聯想官方授權專賣店</t>
+  </si>
+  <si>
+    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0004NTW/i7-13620H/8G+16G/512G+512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>$ 24,900</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gxj9mey7kmw/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0000RTW/i5-13420H/8G+8G/512G/W11/灰)</t>
+  </si>
+  <si>
+    <t>$ 18,490</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/ge9bwywg7dz/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】微軟M365一年組★14吋R7輕薄筆電(IdeaPad Slim 3/82XL008JTW/R7-5825U/16G/512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gtgej9zwrua/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0000STW/i5-13420H/8G+16G/512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>$ 20,490</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gqq2qcf3cwk/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0000RTW/i5-13420H/8G+16G/512G+512G/W11/灰)</t>
+  </si>
+  <si>
+    <t>$ 21,900</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gqrc9zfxeze/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0004NTW/i7-13620H/8G/512G+512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>$ 20,900</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gmreb2cdjyf/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】14吋i5輕薄筆電(IdeaPad Slim 3/83K0000STW/i5-13420H/8G/512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>$ 17,990</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/g72z28kf2se/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】14吋i5輕薄筆電(IdeaPad Slim 3/83K0000RTW/i5-13420H/8G/512G/W11/灰)</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gxsbtgicuia/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0000STW/i5-13420H/8G+8G/512G/W11/藍)</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gyjyfi6exsm/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
+  </si>
+  <si>
+    <t>HTC VIVE Flow 虛擬實境頭戴裝置</t>
+  </si>
+  <si>
+    <t>HTC VIVE FLOW(VR沉浸式眼鏡) 虛擬實境</t>
+  </si>
+  <si>
+    <t>$ 14,790</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/bzzsuwqasph/?s=0&amp;t=5&amp;f=d&amp;k=htc%20%E8%99%9B%E6%93%AC%20vive%20flow</t>
+  </si>
+  <si>
+    <t>Yahoo拍賣 - 輝煌數碼</t>
+  </si>
+  <si>
+    <t>(含稅附發票可開統編)JC HTC VIVE Flow 虛擬實境頭戴裝置 元宇宙 VR AR 公司貨 現貨免運</t>
+  </si>
+  <si>
+    <t>$ 7,900</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/b9xwxeyw8ff/?s=0&amp;t=5&amp;f=d&amp;k=htc%20%E8%99%9B%E6%93%AC%20vive%20flow</t>
+  </si>
+  <si>
+    <t>蝦皮購物 - JC數位生活</t>
+  </si>
+  <si>
+    <t>(含稅附發票可開統編)JC HTC VIVE Flow 虛擬實境頭戴裝置 元宇宙 VR AR 公司貨</t>
+  </si>
+  <si>
+    <t>$ 11,900</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/bw89qkwgdia/?s=0&amp;t=5&amp;f=d&amp;k=htc%20%E8%99%9B%E6%93%AC%20vive%20flow</t>
+  </si>
+  <si>
+    <t>Yahoo拍賣 - Y7883025886</t>
+  </si>
+  <si>
+    <t>【原廠盒裝】宏達電 HTC VIVE Flow 虛擬實境眼鏡 VR 沉浸式體驗</t>
+  </si>
+  <si>
+    <t>$ 12,990</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/b57bgs8tfux/?s=0&amp;t=5&amp;f=d&amp;k=htc%20%E8%99%9B%E6%93%AC%20vive%20flow</t>
+  </si>
+  <si>
+    <t>Yahoo拍賣 - 港都網路3C生活館</t>
+  </si>
+  <si>
+    <t>Kieslect 藍牙通話智慧運動手錶 kr2</t>
+  </si>
+  <si>
+    <t>KIESLECT 智慧通話運動手錶 Kr2 46.4 x 11.65mm 黑色 1個</t>
+  </si>
+  <si>
+    <t>$ 1,800</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/grasi6c78zi/?s=0&amp;f=d&amp;t=14&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>【Kieslect】藍芽通話智慧運動手錶 Kr2 星空黑 / 銀河灰 - 隨貨附黑色錶帶</t>
+  </si>
+  <si>
+    <t>$ 1,990</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gr8nepsgv6d/?s=0&amp;f=d&amp;t=14&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/grasi6c78zi/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>KIESLECT 智慧通話運動手錶 Kr2 銀灰色 1個 46.4 x 11.65mm</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gtys36dzxv7/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>《原廠 免運 可通話》Kieslect Kr2 雙核心 AMOLED 智慧通話手錶 智慧手錶 智慧手錶 兒童手錶 運動</t>
+  </si>
+  <si>
+    <t>$ 2,080</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gdu8ta92n4i/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>【送原廠充電線】Kieslect Kr2 藍芽通話智慧運動手錶 Kr2 / IP68 / 心律血氧監測</t>
+  </si>
+  <si>
+    <t>$ 1,880</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gggxj2vx8bh/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - Bone Sports 戶外生活</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gr8nepsgv6d/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>Kieslect 藍芽通話智慧運動手錶 kr2 (隨貨附黑色錶帶/IP68/藍芽通話)</t>
+  </si>
+  <si>
+    <t>$ 1,390～2,980</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gr7dasmn5ey/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - 愛美麗福利社 (日立除濕機日立冷氣網路授權經銷商)</t>
+  </si>
+  <si>
+    <t>Kieslect 藍芽通話智慧運動手錶 Kr2 (隨貨附黑色錶帶 / IP68 / 心律血氧監測 / 藍芽通話)</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gg4ndunui5v/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>Kieslect 藍芽通話智慧運動手錶 Kr2 星空黑 / 銀河灰 - 隨貨附黑色錶帶 (銀河灰)</t>
+  </si>
+  <si>
+    <t>$ 2,499</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gimzv92gsjg/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>【加送充電線】Kieslect Kr2 藍芽通話智慧運動手錶 Kr2 / IP68 / 心律血氧監測(隨貨贈黑色錶帶)</t>
+  </si>
+  <si>
+    <t>$ 1,980</t>
+  </si>
+  <si>
+    <t>https://www.findprice.com.tw/go/gs3j8svrp4t/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
+  </si>
+  <si>
+    <t>蝦皮商城 - 來點科技 Have a Tech 鍵盤/滑鼠/攝影機/3C周邊小物</t>
+  </si>
+  <si>
     <t>APPLE MacBook Air M2 8G 256G 15吋 太空灰</t>
-  </si>
-  <si>
-    <t>$ 41,590</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gsbi935fxxn/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>APPLE MacBook Air M2 8G 256G 15吋 銀 MQKR3TA/A</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gcfjx8zdqcs/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>APPLE MacBook Air M2 8G 256G 13吋 午夜 MLY33TA/A</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gfmfz827zeh/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>APPLE MacBook Air M2 8G 256G 15吋 星光 MQKU3TA/A</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gm72j7csdnt/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>APPLE MacBook Air M2 8G 256G 15吋 午夜 MQKW3TA/A</t>
-  </si>
-  <si>
-    <t>$ 42,500</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gebmj29ghtv/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>APPLE MacBook Air M2 8G 256G 13吋 星光 MLY13TA/A</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/grvdgddrwbu/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M2/8G/512G/太空灰 MLXX3TA/A 限量促銷</t>
-  </si>
-  <si>
-    <t>$ 45,100</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/ga6zndsxxei/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>樂天市場 - COMDEX印表機專賣店</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/ghhh59ep57m/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>蝦皮購物精選 - 點子3C 二手3C專賣店</t>
-  </si>
-  <si>
-    <t>全館最高折1000元「點子3C」Apple MacBook Air 15吋 M2 8G 256G 2023年 A2941</t>
-  </si>
-  <si>
-    <t>$ 20,580</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gwzwj6ahnwx/?s=0&amp;t=1&amp;f=d&amp;k=apple%20macbook%20air%20m2</t>
-  </si>
-  <si>
-    <t>Apple 原廠 MagSafe 充電器</t>
-  </si>
-  <si>
-    <t>【Apple】原廠新款 MagSafe 充電器 - 1公尺 (A2580)</t>
-  </si>
-  <si>
-    <t>$ 1,250</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gz3advj5jhr/?s=0&amp;f=d&amp;t=14&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>鮮拾</t>
-  </si>
-  <si>
-    <t>【Apple】原廠MagSafe充電器</t>
-  </si>
-  <si>
-    <t>$ 1,238</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gfzsv8izum9/?s=0&amp;f=d&amp;t=14&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gfzsv8izum9/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple 原廠公司貨A3250 / MagSafe 充電器-200cm (2024新款盒裝)</t>
-  </si>
-  <si>
-    <t>$ 1,613</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g56tmnahe7y/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>【Apple】原廠新款 MagSafe 充電器 - 2公尺 (A3250)</t>
-  </si>
-  <si>
-    <t>$ 1,750</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gn7bsf234j3/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>【全新品 包裝已拆】Apple 原廠 MagSafe 充電器 MHXH3TA/A (臺灣公司貨)</t>
-  </si>
-  <si>
-    <t>$ 1,099</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/geey8ie436g/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>樂天市場 - Mr ORIGINAL</t>
-  </si>
-  <si>
-    <t>Apple 原廠 MagSafe 充電器 A3502</t>
-  </si>
-  <si>
-    <t>$ 1,260</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gaxzhwtg2js/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple 原廠 MagSafe 充電器 (2 公尺) A3502</t>
-  </si>
-  <si>
-    <t>$ 1,760</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gevqz8p82nc/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple 原廠 MagSafe 充電器 1m (MX6X3TA/A) 白</t>
-  </si>
-  <si>
-    <t>$ 1,290</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g4begc6962j/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>myfone 網路門市</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gz3advj5jhr/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple原廠 MagSafe充電器1m (MX6X3TA/A)-白</t>
-  </si>
-  <si>
-    <t>$ 1,190</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g3pvzxcp5u6/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple 原廠公司貨A2580 / MagSafe 充電器-100cm (2024新款盒裝)</t>
-  </si>
-  <si>
-    <t>$ 1,135</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gcjsttf223z/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gfk99njxnpz/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>蝦皮購物精選 - CASESSI 購物</t>
-  </si>
-  <si>
-    <t>Apple 蘋果保固一年 新款MagSafe 充電器-2M / A3250【原廠盒裝】</t>
-  </si>
-  <si>
-    <t>$ 1,612</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g4f32iutdmy/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple 蘋果 原廠新款 MagSafe 充電器 - 1公尺 (A2580)</t>
-  </si>
-  <si>
-    <t>$ 1,218</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/giy8rjzrkhc/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Global Mall 環球 Online</t>
-  </si>
-  <si>
-    <t>Apple蘋果 臺灣原廠官方正品 MagSafe 充電器 (1 公尺)【原廠保固一年】A2580 / 2024最新款</t>
-  </si>
-  <si>
-    <t>$ 1,289</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gp5td25ppac/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - NOKIA品牌專賣店</t>
-  </si>
-  <si>
-    <t>Apple MagSafe Charger 充電器 原廠 公司貨 保證正品</t>
-  </si>
-  <si>
-    <t>$ 950</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gi6vrdy6vyc/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - Mr.Reset | 3C 福利品的銷售專家</t>
-  </si>
-  <si>
-    <t>Apple 原廠 MagSafe 雙充電器 (MHXF3TA/A) 展示品</t>
-  </si>
-  <si>
-    <t>$ 2,600</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/ge4u8kk6up8/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>$ 1,136</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gdu92tv8xqa/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple 蘋果保固一年 新款MagSafe 充電器-1M / A2580【原廠盒裝】</t>
-  </si>
-  <si>
-    <t>$ 1,134</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gbvg9uz2px7/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple 臺灣原廠盒裝新款 MagSafe 充電器-1M【A2580】支援iPhone 17/16系列</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gp5kwh4xypu/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>Apple 蘋果 原廠新款 MagSafe 充電器 - 2公尺 (A3250)</t>
-  </si>
-  <si>
-    <t>$ 1,614</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gmzcxqaesp6/?s=0&amp;t=1&amp;f=d&amp;k=apple%20%E5%8E%9F%E5%BB%A0%20magsafe%20%E5%85%85%E9%9B%BB%20%E5%99%A8</t>
-  </si>
-  <si>
-    <t>OPPO Reno8 Pro 5G</t>
-  </si>
-  <si>
-    <t>【OPPO】A級福利品 Reno8 Pro 5G 6.7吋(12G/256G)</t>
-  </si>
-  <si>
-    <t>$ 5,590</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g9yptu4svqi/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20reno8%20pro%205g</t>
-  </si>
-  <si>
-    <t>$ 5,211</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g75seveppud/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%20pro%205g</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g9yptu4svqi/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%20pro%205g</t>
-  </si>
-  <si>
-    <t>OPPO Reno8 Pro 12G/256G 6.7吋 5G 智慧手機 公司貨 Reno 8 福利品【ET手機倉庫】</t>
-  </si>
-  <si>
-    <t>$ 5,590～7,500</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g4w88rwr3xt/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%20pro%205g</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - ET手機倉庫</t>
-  </si>
-  <si>
-    <t>博客來</t>
-  </si>
-  <si>
-    <t>【樂曄通訊】OPPO Reno8 Pro 5G 12G/256G 凝光綠 6.7吋 超級閃充 超強夜拍 全新未拆保固一年</t>
-  </si>
-  <si>
-    <t>$ 16,200</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gbjfsb3v8ki/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%20pro%205g</t>
-  </si>
-  <si>
-    <t>OPPO Reno8 5G</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g75seveppud/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>【OPPO】Reno8 (12G/256G) 5G 智慧手機 (S+級福利品)</t>
-  </si>
-  <si>
-    <t>$ 4,811</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gbwdkma64nu/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>【樂曄通訊】OPPO Reno8 T 5G 8GB/128GB 首款億級畫素 6.7吋 67W超級閃充 全新未拆一年保固</t>
-  </si>
-  <si>
-    <t>$ 8,500</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g8z556jvhqk/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>OPPO Reno8 8G/256G 6.4吋 5G 智慧手機 Reno 8 福利品【ET手機倉庫】</t>
-  </si>
-  <si>
-    <t>$ 5,500～7,300</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gjr9uw7244w/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>【賀運福利品】OPPO Reno8 5G 6.4吋</t>
-  </si>
-  <si>
-    <t>$ 3,611～3,811</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gwifu8n9cd2/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - Hold Win賀運認證福利機</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gbwdkma64nu/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>【OPPO】B+級福利品 Reno8 5G 6.4吋(8G/256G)</t>
-  </si>
-  <si>
-    <t>$ 3,411</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/ggzst3nzjxh/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g75seveppud/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>【OPPO】A+級福利品 Reno8 5G 6.4吋(8G/256G)</t>
-  </si>
-  <si>
-    <t>$ 4,999</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g8zqmkddw9f/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>【OPPO】A級福利品 Reno8 5G 6.4吋(12G/256G)</t>
-  </si>
-  <si>
-    <t>$ 5,300</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gzg9k7i5m77/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g9yptu4svqi/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>$ 3,911</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gmvmp7men9d/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>【OPPO】A級福利品 Reno8 5G 6.4吋(8G/256G)</t>
-  </si>
-  <si>
-    <t>$ 3,711</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gpn6yxef4vh/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20reno8%205g</t>
-  </si>
-  <si>
-    <t>OPPO A77 5G</t>
-  </si>
-  <si>
-    <t>【OPPO】【A級福利品】OPPO A77 (5G) (4+64GB)</t>
-  </si>
-  <si>
-    <t>$ 3,111</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gxthgfpwh3i/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20a77%205g</t>
-  </si>
-  <si>
-    <t>【OPPO】A級福利品 A77 5G 6.5吋(4G/64G)</t>
-  </si>
-  <si>
-    <t>$ 2,611</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g4ta9digtgn/?s=0&amp;f=d&amp;t=14&amp;k=oppo%20a77%205g</t>
-  </si>
-  <si>
-    <t>【創宇通訊│全新品】OPPO A77 6+128GB 6.5吋 (5G) 臉部解鎖 雙卡雙待 超級閃充 大電量</t>
-  </si>
-  <si>
-    <t>$ 4,990</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gf2gawdgshm/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g4ta9digtgn/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
-  </si>
-  <si>
-    <t>【OPPO】A級福利品 A77 5G 6.5吋(6G/128G)</t>
-  </si>
-  <si>
-    <t>$ 2,911</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/ggq7kh93e8b/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gxthgfpwh3i/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
-  </si>
-  <si>
-    <t>【OPPO】A+級福利品 OPPO A77 5G 6.5吋(4G/64G)</t>
-  </si>
-  <si>
-    <t>$ 3,332</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gcmy9tnkn3t/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
-  </si>
-  <si>
-    <t>OPPO A77 (5G) 64GB 安卓13 4800萬畫素</t>
-  </si>
-  <si>
-    <t>$ 2,000</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g2p6ywmtbqz/?s=0&amp;t=1&amp;f=d&amp;k=oppo%20a77%205g</t>
-  </si>
-  <si>
-    <t>蝦皮購物精選 - 我❤️香機寶</t>
-  </si>
-  <si>
-    <t>Lenovo IdeaPad Slim 3 14吋筆電</t>
-  </si>
-  <si>
-    <t>【Lenovo】14吋R7輕薄筆電(IdeaPad Slim 3/82XL008KTW/R7-5825U/16G/512G/W11/灰)</t>
-  </si>
-  <si>
-    <t>$ 14,111</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gvmqhzy2e76/?s=0&amp;f=d&amp;t=14&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>Lenovo 聯想 IdeaPad Slim 3 輕薄筆電 14吋 灰色 i5-13420H 512GB 8GB WIN11 Home IdeaPad Slim 3 14IRH10</t>
-  </si>
-  <si>
-    <t>$ 21,990</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gc9pmg8xnzc/?s=0&amp;f=d&amp;t=14&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】14吋i5輕薄筆電(IdeaPad Slim 3/83EL0017TW/i5-13420H/16G/512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>$ 15,111</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gtgquij3ivv/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gvmqhzy2e76/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】14吋R7輕薄筆電(IdeaPad Slim 3/82XL008JTW/R7-5825U/16G/512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gebbk96vkmr/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】Office 2024組★14吋R7輕薄筆電(IdeaPad Slim 3/82XL008JTW/R7-5825U/16G/512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>$ 18,301</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g975tdrbguk/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】微軟M365一年組★14吋R7輕薄筆電(IdeaPad Slim 3/82XL008KTW/R7-5825U/16G/512G/W11/灰)</t>
-  </si>
-  <si>
-    <t>$ 20,390</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gizwb3nk7w4/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】Office 2024組★14吋R7輕薄筆電(IdeaPad Slim 3/82XL008KTW/R7-5825U/16G/512G/W11/灰)</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gq9kc3ucrt3/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】Office 2024組★14吋i5輕薄筆電(IdeaPad Slim 3/83EL0017TW/i5-13420H/16G/512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>$ 20,301</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gbe6scefp6n/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>Lenovo IdeaPad Slim 3 83K000AGTW 14吋 輕薄效能筆電</t>
-  </si>
-  <si>
-    <t>$ 16,490</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/guek92saz4p/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - 崑碁電腦專賣店</t>
-  </si>
-  <si>
-    <t>Lenovo 聯想 IdeaPad Slim 3 83K000AGTW i5/14吋 效能筆電[聊聊再優惠]</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g7ckkgzmr86/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - Kunchi崑碁電腦3C選品店</t>
-  </si>
-  <si>
-    <t>Lenovo 聯想 IdeaPad Slim 3 83EL0017TW i5/16G/512G 14吋輕薄筆電[聊聊再優</t>
-  </si>
-  <si>
-    <t>$ 16,990</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gpewszgc4si/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>Lenovo 聯想 IdeaPad Slim 3 83K90013TW R7-8840HS 14吋 輕薄筆電</t>
-  </si>
-  <si>
-    <t>$ 19,990</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gy9iuv4diwb/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - Lenovo｜聯想官方授權專賣店</t>
-  </si>
-  <si>
-    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0004NTW/i7-13620H/8G+16G/512G+512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>$ 24,900</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gxj9mey7kmw/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0000RTW/i5-13420H/8G+8G/512G/W11/灰)</t>
-  </si>
-  <si>
-    <t>$ 18,490</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/ge9bwywg7dz/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】微軟M365一年組★14吋R7輕薄筆電(IdeaPad Slim 3/82XL008JTW/R7-5825U/16G/512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gtgej9zwrua/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0000STW/i5-13420H/8G+16G/512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>$ 20,490</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gqq2qcf3cwk/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0000RTW/i5-13420H/8G+16G/512G+512G/W11/灰)</t>
-  </si>
-  <si>
-    <t>$ 21,900</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gqrc9zfxeze/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0004NTW/i7-13620H/8G/512G+512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>$ 20,900</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gmreb2cdjyf/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】14吋i5輕薄筆電(IdeaPad Slim 3/83K0000STW/i5-13420H/8G/512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>$ 17,990</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/g72z28kf2se/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】14吋i5輕薄筆電(IdeaPad Slim 3/83K0000RTW/i5-13420H/8G/512G/W11/灰)</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gxsbtgicuia/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>【Lenovo】特仕版 14吋輕薄筆電(IdeaPad Slim 3 83K0000STW/i5-13420H/8G+8G/512G/W11/藍)</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gyjyfi6exsm/?s=0&amp;t=1&amp;f=d&amp;k=slim-3%20lenovo%20%E7%AD%86%E9%9B%BB%2014%E5%90%8B</t>
-  </si>
-  <si>
-    <t>HTC VIVE Flow 虛擬實境頭戴裝置</t>
-  </si>
-  <si>
-    <t>HTC VIVE FLOW(VR沉浸式眼鏡) 虛擬實境</t>
-  </si>
-  <si>
-    <t>$ 14,790</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/bzzsuwqasph/?s=0&amp;t=5&amp;f=d&amp;k=htc%20%E8%99%9B%E6%93%AC%20vive%20flow</t>
-  </si>
-  <si>
-    <t>Yahoo拍賣 - 輝煌數碼</t>
-  </si>
-  <si>
-    <t>(含稅附發票可開統編)JC HTC VIVE Flow 虛擬實境頭戴裝置 元宇宙 VR AR 公司貨 現貨免運</t>
-  </si>
-  <si>
-    <t>$ 7,900</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/b9xwxeyw8ff/?s=0&amp;t=5&amp;f=d&amp;k=htc%20%E8%99%9B%E6%93%AC%20vive%20flow</t>
-  </si>
-  <si>
-    <t>蝦皮購物 - JC數位生活</t>
-  </si>
-  <si>
-    <t>(含稅附發票可開統編)JC HTC VIVE Flow 虛擬實境頭戴裝置 元宇宙 VR AR 公司貨</t>
-  </si>
-  <si>
-    <t>$ 11,900</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/bw89qkwgdia/?s=0&amp;t=5&amp;f=d&amp;k=htc%20%E8%99%9B%E6%93%AC%20vive%20flow</t>
-  </si>
-  <si>
-    <t>Yahoo拍賣 - Y7883025886</t>
-  </si>
-  <si>
-    <t>【原廠盒裝】宏達電 HTC VIVE Flow 虛擬實境眼鏡 VR 沉浸式體驗</t>
-  </si>
-  <si>
-    <t>$ 12,990</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/b57bgs8tfux/?s=0&amp;t=5&amp;f=d&amp;k=htc%20%E8%99%9B%E6%93%AC%20vive%20flow</t>
-  </si>
-  <si>
-    <t>Yahoo拍賣 - 港都網路3C生活館</t>
-  </si>
-  <si>
-    <t>Kieslect 藍牙通話智慧運動手錶 kr2</t>
-  </si>
-  <si>
-    <t>KIESLECT 智慧通話運動手錶 Kr2 46.4 x 11.65mm 黑色 1個</t>
-  </si>
-  <si>
-    <t>$ 1,800</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/grasi6c78zi/?s=0&amp;f=d&amp;t=14&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>【Kieslect】藍芽通話智慧運動手錶 Kr2 星空黑 / 銀河灰 - 隨貨附黑色錶帶</t>
-  </si>
-  <si>
-    <t>$ 1,990</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gr8nepsgv6d/?s=0&amp;f=d&amp;t=14&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/grasi6c78zi/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>KIESLECT 智慧通話運動手錶 Kr2 銀灰色 1個 46.4 x 11.65mm</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gtys36dzxv7/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>《原廠 免運 可通話》Kieslect Kr2 雙核心 AMOLED 智慧通話手錶 智慧手錶 智慧手錶 兒童手錶 運動</t>
-  </si>
-  <si>
-    <t>$ 2,080</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gdu8ta92n4i/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>【送原廠充電線】Kieslect Kr2 藍芽通話智慧運動手錶 Kr2 / IP68 / 心律血氧監測</t>
-  </si>
-  <si>
-    <t>$ 1,880</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gggxj2vx8bh/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - Bone Sports 戶外生活</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gr8nepsgv6d/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>Kieslect 藍芽通話智慧運動手錶 kr2 (隨貨附黑色錶帶/IP68/藍芽通話)</t>
-  </si>
-  <si>
-    <t>$ 1,390～2,980</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gr7dasmn5ey/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - 愛美麗福利社 (日立除濕機日立冷氣網路授權經銷商)</t>
-  </si>
-  <si>
-    <t>Kieslect 藍芽通話智慧運動手錶 Kr2 (隨貨附黑色錶帶 / IP68 / 心律血氧監測 / 藍芽通話)</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gg4ndunui5v/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>Kieslect 藍芽通話智慧運動手錶 Kr2 星空黑 / 銀河灰 - 隨貨附黑色錶帶 (銀河灰)</t>
-  </si>
-  <si>
-    <t>$ 2,499</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gimzv92gsjg/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>【加送充電線】Kieslect Kr2 藍芽通話智慧運動手錶 Kr2 / IP68 / 心律血氧監測(隨貨贈黑色錶帶)</t>
-  </si>
-  <si>
-    <t>$ 1,980</t>
-  </si>
-  <si>
-    <t>https://www.findprice.com.tw/go/gs3j8svrp4t/?s=0&amp;t=1&amp;f=d&amp;k=kr2%20kieslect%20%E6%89%8B%E9%8C%B6%20%E9%81%8B%E5%8B%95</t>
-  </si>
-  <si>
-    <t>蝦皮商城 - 來點科技 Have a Tech 鍵盤/滑鼠/攝影機/3C周邊小物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1289,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.625" customWidth="1"/>
@@ -1348,23 +1349,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-    </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
@@ -1382,55 +1366,21 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1438,16 +1388,16 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1455,13 +1405,13 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
@@ -1472,13 +1422,13 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -1489,16 +1439,16 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1506,13 +1456,13 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -1523,13 +1473,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>307</v>
       </c>
       <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>48</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -1540,13 +1490,13 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -1557,13 +1507,13 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -1574,16 +1524,16 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1591,16 +1541,16 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1608,132 +1558,132 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
         <v>63</v>
       </c>
-      <c r="B24" t="s">
-        <v>72</v>
-      </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E27" t="s">
         <v>31</v>
@@ -1741,237 +1691,237 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
         <v>63</v>
       </c>
-      <c r="B33" t="s">
-        <v>96</v>
-      </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E36" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E41" t="s">
         <v>31</v>
@@ -1979,271 +1929,271 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E42" t="s">
         <v>31</v>
       </c>
     </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D44" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E44" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>129</v>
-      </c>
-      <c r="B46" t="s">
-        <v>130</v>
-      </c>
-      <c r="C46" t="s">
-        <v>131</v>
-      </c>
-      <c r="D46" t="s">
-        <v>135</v>
-      </c>
-      <c r="E46" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" t="s">
         <v>129</v>
       </c>
-      <c r="B47" t="s">
-        <v>136</v>
-      </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E47" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" t="s">
         <v>129</v>
       </c>
-      <c r="B48" t="s">
-        <v>141</v>
-      </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D48" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>144</v>
-      </c>
-      <c r="B52" t="s">
-        <v>149</v>
-      </c>
-      <c r="C52" t="s">
-        <v>150</v>
-      </c>
-      <c r="D52" t="s">
-        <v>151</v>
-      </c>
-      <c r="E52" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>143</v>
+      </c>
+      <c r="B53" t="s">
+        <v>129</v>
+      </c>
+      <c r="C53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" t="s">
         <v>144</v>
       </c>
-      <c r="B53" t="s">
-        <v>152</v>
-      </c>
-      <c r="C53" t="s">
-        <v>153</v>
-      </c>
-      <c r="D53" t="s">
-        <v>154</v>
-      </c>
       <c r="E53" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D54" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>158</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D55" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D56" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B57" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C57" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="D57" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E57" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D58" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B59" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E59" t="s">
         <v>13</v>
@@ -2251,16 +2201,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B60" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D60" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E60" t="s">
         <v>13</v>
@@ -2268,16 +2218,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B61" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C61" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D61" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E61" t="s">
         <v>13</v>
@@ -2285,101 +2235,101 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B62" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C62" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D62" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E62" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>143</v>
+      </c>
+      <c r="B63" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" t="s">
+        <v>169</v>
+      </c>
+      <c r="E63" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="B64" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C64" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D64" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E64" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C65" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D65" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E65" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>176</v>
-      </c>
-      <c r="B66" t="s">
-        <v>183</v>
-      </c>
-      <c r="C66" t="s">
-        <v>184</v>
-      </c>
-      <c r="D66" t="s">
-        <v>185</v>
-      </c>
-      <c r="E66" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>175</v>
+      </c>
+      <c r="B67" t="s">
         <v>176</v>
       </c>
-      <c r="B67" t="s">
-        <v>180</v>
-      </c>
       <c r="C67" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E67" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B68" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C68" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D68" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E68" t="s">
         <v>13</v>
@@ -2387,33 +2337,33 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B69" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C69" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D69" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E69" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B70" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C70" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D70" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
         <v>13</v>
@@ -2421,33 +2371,50 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>175</v>
+      </c>
+      <c r="B71" t="s">
+        <v>186</v>
+      </c>
+      <c r="C71" t="s">
+        <v>187</v>
+      </c>
+      <c r="D71" t="s">
+        <v>188</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>175</v>
+      </c>
+      <c r="B72" t="s">
         <v>176</v>
       </c>
-      <c r="B71" t="s">
-        <v>194</v>
-      </c>
-      <c r="C71" t="s">
-        <v>195</v>
-      </c>
-      <c r="D71" t="s">
-        <v>196</v>
-      </c>
-      <c r="E71" t="s">
-        <v>197</v>
+      <c r="C72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D72" t="s">
+        <v>189</v>
+      </c>
+      <c r="E72" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="B73" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C73" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D73" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E73" t="s">
         <v>13</v>
@@ -2455,50 +2422,33 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="B74" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D74" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E74" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>198</v>
-      </c>
-      <c r="B75" t="s">
-        <v>205</v>
-      </c>
-      <c r="C75" t="s">
-        <v>206</v>
-      </c>
-      <c r="D75" t="s">
-        <v>207</v>
-      </c>
-      <c r="E75" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>197</v>
+      </c>
+      <c r="B76" t="s">
         <v>198</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>199</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>200</v>
-      </c>
-      <c r="D76" t="s">
-        <v>208</v>
       </c>
       <c r="E76" t="s">
         <v>13</v>
@@ -2506,33 +2456,33 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C77" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D77" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B78" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C78" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D78" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E78" t="s">
         <v>13</v>
@@ -2540,16 +2490,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>197</v>
+      </c>
+      <c r="B79" t="s">
         <v>198</v>
       </c>
-      <c r="B79" t="s">
-        <v>214</v>
-      </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="D79" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E79" t="s">
         <v>13</v>
@@ -2557,16 +2507,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B80" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C80" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D80" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E80" t="s">
         <v>13</v>
@@ -2574,16 +2524,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B81" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C81" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D81" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E81" t="s">
         <v>13</v>
@@ -2591,135 +2541,135 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B82" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C82" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D82" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E82" t="s">
-        <v>225</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B83" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C83" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D83" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E83" t="s">
-        <v>228</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B84" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C84" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D84" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E84" t="s">
-        <v>228</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B85" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C85" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D85" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E85" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B86" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C86" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D86" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="E86" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B87" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C87" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="D87" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E87" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B88" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C88" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D88" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E88" t="s">
-        <v>13</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B89" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C89" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D89" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E89" t="s">
         <v>13</v>
@@ -2727,16 +2677,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B90" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C90" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D90" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E90" t="s">
         <v>13</v>
@@ -2744,16 +2694,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B91" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C91" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="D91" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E91" t="s">
         <v>13</v>
@@ -2761,16 +2711,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B92" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C92" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D92" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E92" t="s">
         <v>13</v>
@@ -2778,16 +2728,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B93" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C93" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D93" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="E93" t="s">
         <v>13</v>
@@ -2795,152 +2745,152 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C94" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D94" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E94" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>197</v>
+      </c>
+      <c r="B95" t="s">
+        <v>252</v>
+      </c>
+      <c r="C95" t="s">
+        <v>253</v>
+      </c>
+      <c r="D95" t="s">
+        <v>254</v>
+      </c>
+      <c r="E95" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c r="B96" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D96" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E96" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c r="B97" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C97" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="D97" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E97" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>260</v>
-      </c>
-      <c r="B98" t="s">
-        <v>269</v>
-      </c>
-      <c r="C98" t="s">
-        <v>270</v>
-      </c>
-      <c r="D98" t="s">
-        <v>271</v>
-      </c>
-      <c r="E98" t="s">
-        <v>272</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>259</v>
+      </c>
+      <c r="B99" t="s">
         <v>260</v>
       </c>
-      <c r="B99" t="s">
-        <v>273</v>
-      </c>
       <c r="C99" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="D99" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="E99" t="s">
-        <v>276</v>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>259</v>
+      </c>
+      <c r="B100" t="s">
+        <v>264</v>
+      </c>
+      <c r="C100" t="s">
+        <v>265</v>
+      </c>
+      <c r="D100" t="s">
+        <v>266</v>
+      </c>
+      <c r="E100" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="B101" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C101" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D101" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="E101" t="s">
-        <v>6</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="B102" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C102" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D102" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E102" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>277</v>
-      </c>
-      <c r="B103" t="s">
-        <v>278</v>
-      </c>
-      <c r="C103" t="s">
-        <v>279</v>
-      </c>
-      <c r="D103" t="s">
-        <v>284</v>
-      </c>
-      <c r="E103" t="s">
-        <v>6</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>276</v>
+      </c>
+      <c r="B104" t="s">
         <v>277</v>
       </c>
-      <c r="B104" t="s">
-        <v>285</v>
-      </c>
       <c r="C104" t="s">
+        <v>278</v>
+      </c>
+      <c r="D104" t="s">
         <v>279</v>
-      </c>
-      <c r="D104" t="s">
-        <v>286</v>
       </c>
       <c r="E104" t="s">
         <v>6</v>
@@ -2948,121 +2898,172 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B105" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C105" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D105" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E105" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>276</v>
+      </c>
+      <c r="B106" t="s">
         <v>277</v>
       </c>
-      <c r="B106" t="s">
-        <v>290</v>
-      </c>
       <c r="C106" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="D106" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E106" t="s">
-        <v>293</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B107" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C107" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D107" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E107" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B108" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C108" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D108" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E108" t="s">
-        <v>298</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B109" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C109" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D109" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E109" t="s">
-        <v>18</v>
+        <v>292</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B110" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="C110" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="D110" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="E110" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B111" t="s">
+        <v>294</v>
+      </c>
+      <c r="C111" t="s">
+        <v>295</v>
+      </c>
+      <c r="D111" t="s">
+        <v>296</v>
+      </c>
+      <c r="E111" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>276</v>
+      </c>
+      <c r="B112" t="s">
+        <v>298</v>
+      </c>
+      <c r="C112" t="s">
+        <v>281</v>
+      </c>
+      <c r="D112" t="s">
+        <v>299</v>
+      </c>
+      <c r="E112" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>276</v>
+      </c>
+      <c r="B113" t="s">
+        <v>300</v>
+      </c>
+      <c r="C113" t="s">
+        <v>301</v>
+      </c>
+      <c r="D113" t="s">
+        <v>302</v>
+      </c>
+      <c r="E113" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>276</v>
+      </c>
+      <c r="B114" t="s">
+        <v>303</v>
+      </c>
+      <c r="C114" t="s">
         <v>304</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D114" t="s">
         <v>305</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E114" t="s">
         <v>306</v>
-      </c>
-      <c r="E111" t="s">
-        <v>307</v>
       </c>
     </row>
   </sheetData>
